--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/TEXAS_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/TEXAS_2013.xlsx
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C182">
@@ -4243,7 +4243,7 @@
         <v>201</v>
       </c>
       <c r="D216">
-        <v>0.000963437314263</v>
+        <v>0.0009634373142630002</v>
       </c>
     </row>
     <row r="217">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C257">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C412">
@@ -9661,7 +9661,7 @@
         <v>203</v>
       </c>
       <c r="D517">
-        <v>0.000973023755201</v>
+        <v>0.0009730237552010002</v>
       </c>
     </row>
     <row r="518">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C917">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1102">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1103">
@@ -21174,7 +21174,7 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1157">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1164">
@@ -24936,7 +24936,7 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1366">
@@ -28561,7 +28561,7 @@
         <v>203</v>
       </c>
       <c r="D1567">
-        <v>0.000973023755201</v>
+        <v>0.0009730237552010002</v>
       </c>
     </row>
     <row r="1568">
@@ -31002,7 +31002,7 @@
       </c>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1703">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="B1743" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1743">
@@ -33655,7 +33655,7 @@
         <v>203</v>
       </c>
       <c r="D1850">
-        <v>0.000973023755201</v>
+        <v>0.0009730237552010002</v>
       </c>
     </row>
     <row r="1851">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B1924" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1924">
